--- a/example_data/sample_metadata.xlsx
+++ b/example_data/sample_metadata.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\nanastasiadou\Bioinfo\Projects\NatStuff\Seq2Viz\example_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natan\Υπολογιστής\Bioinfo\Projects\NatStuff\Seq2Viz\example_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68171E05-7973-4B3A-9168-8BF8D3A314C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520"/>
   </bookViews>
   <sheets>
     <sheet name="Φύλλο1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
   <si>
     <t>control</t>
   </si>
@@ -67,13 +66,16 @@
   </si>
   <si>
     <t>Group</t>
+  </si>
+  <si>
+    <t>Age</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,7 +102,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,18 +125,32 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -465,16 +481,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -484,8 +500,11 @@
       <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -495,8 +514,11 @@
       <c r="C2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -506,8 +528,11 @@
       <c r="C3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -517,8 +542,11 @@
       <c r="C4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -528,8 +556,11 @@
       <c r="C5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -539,8 +570,11 @@
       <c r="C6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -549,6 +583,9 @@
       </c>
       <c r="C7" t="s">
         <v>12</v>
+      </c>
+      <c r="D7">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/example_data/sample_metadata.xlsx
+++ b/example_data/sample_metadata.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
   <si>
     <t>control</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Age</t>
+  </si>
+  <si>
+    <t>Batch</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="16.296875" bestFit="1" customWidth="1"/>
@@ -490,7 +493,7 @@
     <col min="3" max="3" width="8.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -503,8 +506,11 @@
       <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -517,8 +523,11 @@
       <c r="D2">
         <v>24</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -531,8 +540,11 @@
       <c r="D3">
         <v>24</v>
       </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -545,8 +557,11 @@
       <c r="D4">
         <v>35</v>
       </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -559,8 +574,11 @@
       <c r="D5">
         <v>35</v>
       </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -573,8 +591,11 @@
       <c r="D6">
         <v>70</v>
       </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -586,6 +607,9 @@
       </c>
       <c r="D7">
         <v>70</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
